--- a/nr-rm-adeli/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/nr-rm-adeli/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-06T10:53:29+00:00</t>
+    <t>2024-10-29T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>88</v>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>88</v>
@@ -11737,7 +11737,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>88</v>
